--- a/docs/tabulka-smutek.xlsx
+++ b/docs/tabulka-smutek.xlsx
@@ -1,10 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1414F89E-7579-4FF5-91D9-B0E6AD87BF5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="List1" state="visible" r:id="rId4"/>
+    <sheet name="List1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
@@ -13,77 +17,349 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
-    <t>Je mi smutno</t>
-  </si>
-  <si>
     <t>Je/. mi/. smut/. no/.</t>
   </si>
   <si>
-    <t>Nikdo mi nerozumí</t>
-  </si>
-  <si>
     <t>Nik/. do/. mi/. ne/. ro/. zu/. mí/-</t>
   </si>
   <si>
-    <t>Tečou mi slzy</t>
-  </si>
-  <si>
-    <t>Te/. čou/. mi/. sl/. zy/.</t>
-  </si>
-  <si>
-    <t>Dnes je šedivý den</t>
-  </si>
-  <si>
-    <t>Dnes/. je/. še/. di/. vý/- den/.</t>
-  </si>
-  <si>
-    <t>Je mi těžko</t>
-  </si>
-  <si>
-    <t>Je/. mi/. těž/. ko/.</t>
-  </si>
-  <si>
-    <t>Trochu mě to mrzí</t>
-  </si>
-  <si>
     <t>Tro/. chu/. mě/. to/. mr/. zí/-</t>
   </si>
   <si>
-    <t>Nic se mi nechce dělat</t>
-  </si>
-  <si>
     <t>Nic/. se/. mi/. nech/. ce/. dě/. lat/.</t>
   </si>
   <si>
-    <t>Nálada mi klesla</t>
-  </si>
-  <si>
-    <t>Ná/- la/. da/. mi/. kles/ la/.</t>
-  </si>
-  <si>
-    <t>Cítím se unavený</t>
-  </si>
-  <si>
     <t>Cí/- tím/- se/. u/. na/. ve/. ný/-</t>
   </si>
   <si>
-    <t>Dnes nejsem ve své kůži</t>
-  </si>
-  <si>
     <t>Dnes/. nej/. sem/. ve/. své/- ků/- ži/.</t>
+  </si>
+  <si>
+    <t>Ach/. jo/.</t>
+  </si>
+  <si>
+    <t>Dnes/. je/. oš/. kli/. vo/.</t>
+  </si>
+  <si>
+    <t>Bo/. lí/- mě/. to/.</t>
+  </si>
+  <si>
+    <t>Ne/. mám/- na/. to/. ná/- la/. du/.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Je </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>mi</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> smutno</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Ach</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> jo</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Nic</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> se mi nechce dělat</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Nemám</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> na to náladu</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Cítím se </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>unavený</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Dnes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> nejsem ve své kůži</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Nikdo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> mi nerozumí</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Dnes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>je</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ošklivo</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Bolí </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>mě</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>to</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Trochu </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>mě</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>mrzí</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -106,11 +382,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normální" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -446,41 +723,41 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B10"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="49.142857142857146" customWidth="1"/>
-    <col min="2" max="24" width="13.571428571428571" customWidth="1"/>
+    <col min="1" max="1" width="49.140625" customWidth="1"/>
+    <col min="2" max="24" width="13.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" t="s">
-        <v>3</v>
-      </c>
-    </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>4</v>
+      <c r="A3" s="1" t="s">
+        <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>6</v>
+      <c r="A4" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="B4" t="s">
         <v>7</v>
@@ -488,54 +765,54 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" t="s">
         <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B7" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>14</v>
-      </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>18</v>
+      <c r="A10" s="1" t="s">
+        <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
--- a/docs/tabulka-smutek.xlsx
+++ b/docs/tabulka-smutek.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1414F89E-7579-4FF5-91D9-B0E6AD87BF5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F18AD8EB-D833-427C-B45C-86B5F9310027}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-24465" yWindow="3975" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="List1" sheetId="1" r:id="rId1"/>
@@ -26,9 +26,6 @@
     <t>Tro/. chu/. mě/. to/. mr/. zí/-</t>
   </si>
   <si>
-    <t>Nic/. se/. mi/. nech/. ce/. dě/. lat/.</t>
-  </si>
-  <si>
     <t>Cí/- tím/- se/. u/. na/. ve/. ný/-</t>
   </si>
   <si>
@@ -330,18 +327,29 @@
       </rPr>
       <t>mrzí</t>
     </r>
+  </si>
+  <si>
+    <t>Nic/. se/. mi/. ne/. chce/. dě/. lat/.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -384,7 +392,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normální" xfId="0" builtinId="0"/>
@@ -733,7 +741,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -741,7 +749,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B2" t="s">
         <v>1</v>
@@ -749,31 +757,31 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B6" t="s">
         <v>2</v>
@@ -781,34 +789,34 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>3</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
